--- a/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_PERSONS.xlsx
+++ b/i_test/05_05_test_adding_PROMPT/i_input_xlsx/D3_PERSONS.xlsx
@@ -1,73 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_05_test_adding_PROMPT\i_input_xlsx\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A3B9EA-E55B-409F-B246-E5DACB3A6127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="780" yWindow="840" windowWidth="26610" windowHeight="14130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
-    <t xml:space="preserve">person_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">day_of_birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">month_of_birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year_of_birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">day_of_death</t>
-  </si>
-  <si>
-    <t xml:space="preserve">month_of_death</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year_of_death</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sex_at_instance_creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">race</t>
-  </si>
-  <si>
-    <t xml:space="preserve">country_of_birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_of_birth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_death</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ConCDM_SIM_200421_00001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reliable</t>
+    <t>person_id</t>
+  </si>
+  <si>
+    <t>day_of_birth</t>
+  </si>
+  <si>
+    <t>month_of_birth</t>
+  </si>
+  <si>
+    <t>year_of_birth</t>
+  </si>
+  <si>
+    <t>day_of_death</t>
+  </si>
+  <si>
+    <t>month_of_death</t>
+  </si>
+  <si>
+    <t>year_of_death</t>
+  </si>
+  <si>
+    <t>sex_at_instance_creation</t>
+  </si>
+  <si>
+    <t>race</t>
+  </si>
+  <si>
+    <t>country_of_birth</t>
+  </si>
+  <si>
+    <t>quality</t>
+  </si>
+  <si>
+    <t>date_of_birth</t>
+  </si>
+  <si>
+    <t>date_death</t>
+  </si>
+  <si>
+    <t>ConCDM_SIM_200421_00001</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>month_day_imputed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -103,12 +110,21 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -390,11 +406,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,37 +466,44 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>12</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>9</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>2017</v>
       </c>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
       <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="I2"/>
-      <c r="J2"/>
       <c r="K2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="L2" s="1">
         <v>42990</v>
       </c>
       <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>